--- a/output/证券0820测评功能-评测结果.xlsx
+++ b/output/证券0820测评功能-评测结果.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="20752" windowHeight="9555" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1 " sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="评测记录" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1 " sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评测记录" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1586,7 +1586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="9" min="1" max="1"/>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" s="9">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>AI-007</t>
@@ -1967,6 +1967,100 @@
       <c r="I8" s="11" t="inlineStr">
         <is>
           <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" s="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>AI-008</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>补充</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>快捷服务对话回复</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>回复拼接/文案一致性</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>针对白酒市场行情及相关 ETF 的提问，回复中“您好，我是您的财富专家”被重复输出两次；两段内容直接拼接，前后衔接割裂。</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>同一条回复中开场白只出现一次；多段生成内容合并后应经过统一去重、排序和语义衔接处理。</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>增加回复结果统一后处理，对重复开场白和重复内容进行去重，并优化不同分析段落的衔接。</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>imgs/ai-wealth/ai-wealth-duplicate-greeting.png</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" s="9">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>AI-009</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>补充</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>折价 ETF 选品与分析</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>数据准确性 Bug</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>回复表格内多只 ETF 的实时折溢价率均显示为 0.00%，但详情页显示实际折价率非零，例如恒生医疗 ETF 嘉实为 -1.10%；下方筛选、排序和分析均基于错误数据。</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>表格应准确展示实时折溢价率，并基于真实数据进行筛选、排序和分析；数据不可用时应明确提示。</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>排查折溢价率字段取值、接口映射和默认值处理，增加与详情页数据的一致性校验，避免错误数据继续驱动分析。</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>imgs/ai-wealth/ai-wealth-etf-discount-rate-zero-01.png; imgs/ai-wealth/ai-wealth-etf-discount-rate-zero-02.png; imgs/ai-wealth/ai-wealth-etf-discount-rate-detail-reference.png</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
